--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R62b50d83ec6642ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R70442626e2b44568"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97720477eda944ac"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3611ea586e12496c"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R70442626e2b44568"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rad4154d8439c4ddd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3611ea586e12496c"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0de7b44fc35441e1"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rad4154d8439c4ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6897092714c747d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0de7b44fc35441e1"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14d454e8fb7a47b1"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6897092714c747d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2a74e3a76b0e4cdc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14d454e8fb7a47b1"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4625012f4aec4b08"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2a74e3a76b0e4cdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R663cba740896416d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4625012f4aec4b08"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc54f61bce5304455"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R663cba740896416d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R63835d3dfcf74286"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc54f61bce5304455"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26c7ee6a97724bd7"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R63835d3dfcf74286"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96b3d783ad6e4f22"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26c7ee6a97724bd7"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88dd980e7fb64134"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96b3d783ad6e4f22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R69b22b029e634a93"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88dd980e7fb64134"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra32b619565bb46ce"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R69b22b029e634a93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re950a514c37b4a3c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra32b619565bb46ce"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e59fb961cc747d1"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re950a514c37b4a3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9f3b9cc32bef41cf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e59fb961cc747d1"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5cc4386d5ce41fe"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9f3b9cc32bef41cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbaa2f22a3f2644e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5cc4386d5ce41fe"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5f7c57b8f4844fb"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbaa2f22a3f2644e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0490e540b1c34248"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5f7c57b8f4844fb"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07d7f5e4ae214ffd"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0490e540b1c34248"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rda2392c67eee442d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07d7f5e4ae214ffd"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4578100119ca446f"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rda2392c67eee442d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R895cf47b4acc43a7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4578100119ca446f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3629e53327534564"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/Comments/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R895cf47b4acc43a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re731dee6a4744707"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,6 +92,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3629e53327534564"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f9b4fec0dea40d6"/>
 </x:worksheet>
 </file>